--- a/data/xlsx/bwcci--beautification-and-entrepreneurship-development-residential.xlsx
+++ b/data/xlsx/bwcci--beautification-and-entrepreneurship-development-residential.xlsx
@@ -99,7 +99,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="bottom"/>
@@ -132,6 +132,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -636,7 +642,7 @@
       </c>
     </row>
     <row r="16" ht="14.15" customHeight="1">
-      <c r="A16" s="7" t="n">
+      <c r="A16" s="14" t="n">
         <v>1</v>
       </c>
       <c r="B16" s="8" t="inlineStr">
@@ -647,7 +653,9 @@
       <c r="C16" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D16" s="9" t="n"/>
+      <c r="D16" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E16" s="9" t="n">
         <v>5</v>
       </c>
@@ -658,7 +666,7 @@
       <c r="G16" s="9" t="n"/>
     </row>
     <row r="17" ht="14.15" customHeight="1">
-      <c r="A17" s="7" t="n">
+      <c r="A17" s="14" t="n">
         <v>2</v>
       </c>
       <c r="B17" s="8" t="inlineStr">
@@ -669,7 +677,9 @@
       <c r="C17" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D17" s="9" t="n"/>
+      <c r="D17" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E17" s="9" t="n">
         <v>5</v>
       </c>
@@ -680,7 +690,7 @@
       <c r="G17" s="9" t="n"/>
     </row>
     <row r="18" ht="14.15" customHeight="1">
-      <c r="A18" s="7" t="n">
+      <c r="A18" s="14" t="n">
         <v>3</v>
       </c>
       <c r="B18" s="8" t="inlineStr">
@@ -691,7 +701,9 @@
       <c r="C18" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D18" s="9" t="n"/>
+      <c r="D18" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E18" s="9" t="n">
         <v>5</v>
       </c>
@@ -702,7 +714,7 @@
       <c r="G18" s="9" t="n"/>
     </row>
     <row r="19" ht="14.15" customHeight="1">
-      <c r="A19" s="7" t="n">
+      <c r="A19" s="14" t="n">
         <v>4</v>
       </c>
       <c r="B19" s="8" t="inlineStr">
@@ -713,7 +725,9 @@
       <c r="C19" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D19" s="9" t="n"/>
+      <c r="D19" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E19" s="9" t="n">
         <v>8</v>
       </c>
@@ -724,7 +738,7 @@
       <c r="G19" s="9" t="n"/>
     </row>
     <row r="20" ht="14.15" customHeight="1">
-      <c r="A20" s="7" t="n">
+      <c r="A20" s="14" t="n">
         <v>5</v>
       </c>
       <c r="B20" s="8" t="inlineStr">
@@ -735,7 +749,9 @@
       <c r="C20" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D20" s="9" t="n"/>
+      <c r="D20" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E20" s="9" t="n">
         <v>8</v>
       </c>
@@ -746,7 +762,7 @@
       <c r="G20" s="9" t="n"/>
     </row>
     <row r="21" ht="14.15" customHeight="1">
-      <c r="A21" s="7" t="n">
+      <c r="A21" s="14" t="n">
         <v>6</v>
       </c>
       <c r="B21" s="8" t="inlineStr">
@@ -757,7 +773,9 @@
       <c r="C21" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D21" s="9" t="n"/>
+      <c r="D21" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E21" s="9" t="n">
         <v>8</v>
       </c>
@@ -768,7 +786,7 @@
       <c r="G21" s="9" t="n"/>
     </row>
     <row r="22" ht="14.15" customHeight="1">
-      <c r="A22" s="7" t="n">
+      <c r="A22" s="14" t="n">
         <v>7</v>
       </c>
       <c r="B22" s="8" t="inlineStr">
@@ -779,7 +797,9 @@
       <c r="C22" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D22" s="9" t="n"/>
+      <c r="D22" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E22" s="9" t="n">
         <v>7</v>
       </c>
@@ -790,7 +810,7 @@
       <c r="G22" s="9" t="n"/>
     </row>
     <row r="23" ht="14.15" customHeight="1">
-      <c r="A23" s="7" t="n">
+      <c r="A23" s="14" t="n">
         <v>8</v>
       </c>
       <c r="B23" s="8" t="inlineStr">
@@ -801,7 +821,9 @@
       <c r="C23" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D23" s="9" t="n"/>
+      <c r="D23" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E23" s="9" t="n">
         <v>7</v>
       </c>
@@ -812,7 +834,7 @@
       <c r="G23" s="9" t="n"/>
     </row>
     <row r="24" ht="14.15" customHeight="1">
-      <c r="A24" s="7" t="n">
+      <c r="A24" s="14" t="n">
         <v>9</v>
       </c>
       <c r="B24" s="8" t="inlineStr">
@@ -823,7 +845,9 @@
       <c r="C24" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D24" s="9" t="n"/>
+      <c r="D24" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E24" s="9" t="n">
         <v>8</v>
       </c>
@@ -834,7 +858,7 @@
       <c r="G24" s="9" t="n"/>
     </row>
     <row r="25" ht="14.15" customHeight="1">
-      <c r="A25" s="7" t="n">
+      <c r="A25" s="14" t="n">
         <v>10</v>
       </c>
       <c r="B25" s="8" t="inlineStr">
@@ -845,7 +869,9 @@
       <c r="C25" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D25" s="9" t="n"/>
+      <c r="D25" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E25" s="9" t="n">
         <v>8</v>
       </c>
@@ -856,7 +882,7 @@
       <c r="G25" s="9" t="n"/>
     </row>
     <row r="26" ht="14.15" customHeight="1">
-      <c r="A26" s="7" t="n">
+      <c r="A26" s="14" t="n">
         <v>11</v>
       </c>
       <c r="B26" s="8" t="inlineStr">
@@ -867,7 +893,9 @@
       <c r="C26" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D26" s="9" t="n"/>
+      <c r="D26" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E26" s="9" t="n">
         <v>7</v>
       </c>
@@ -878,7 +906,7 @@
       <c r="G26" s="9" t="n"/>
     </row>
     <row r="27" ht="14.15" customHeight="1">
-      <c r="A27" s="7" t="n">
+      <c r="A27" s="14" t="n">
         <v>12</v>
       </c>
       <c r="B27" s="8" t="inlineStr">
@@ -889,7 +917,9 @@
       <c r="C27" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D27" s="9" t="n"/>
+      <c r="D27" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E27" s="9" t="n">
         <v>7</v>
       </c>
@@ -900,7 +930,7 @@
       <c r="G27" s="9" t="n"/>
     </row>
     <row r="28" ht="14.15" customHeight="1">
-      <c r="A28" s="7" t="n">
+      <c r="A28" s="14" t="n">
         <v>13</v>
       </c>
       <c r="B28" s="8" t="inlineStr">
@@ -911,7 +941,9 @@
       <c r="C28" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D28" s="9" t="n"/>
+      <c r="D28" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E28" s="9" t="n">
         <v>6</v>
       </c>
@@ -922,7 +954,7 @@
       <c r="G28" s="9" t="n"/>
     </row>
     <row r="29" ht="14.15" customHeight="1">
-      <c r="A29" s="7" t="n">
+      <c r="A29" s="14" t="n">
         <v>14</v>
       </c>
       <c r="B29" s="8" t="inlineStr">
@@ -933,7 +965,9 @@
       <c r="C29" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D29" s="9" t="n"/>
+      <c r="D29" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E29" s="9" t="n">
         <v>4</v>
       </c>
@@ -944,7 +978,7 @@
       <c r="G29" s="9" t="n"/>
     </row>
     <row r="30" ht="14.15" customHeight="1">
-      <c r="A30" s="7" t="n">
+      <c r="A30" s="14" t="n">
         <v>15</v>
       </c>
       <c r="B30" s="8" t="inlineStr">
@@ -955,7 +989,9 @@
       <c r="C30" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D30" s="9" t="n"/>
+      <c r="D30" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E30" s="9" t="n">
         <v>6</v>
       </c>
@@ -966,7 +1002,7 @@
       <c r="G30" s="9" t="n"/>
     </row>
     <row r="31" ht="14.15" customHeight="1">
-      <c r="A31" s="7" t="n">
+      <c r="A31" s="14" t="n">
         <v>16</v>
       </c>
       <c r="B31" s="8" t="inlineStr">
@@ -977,7 +1013,9 @@
       <c r="C31" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D31" s="9" t="n"/>
+      <c r="D31" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E31" s="9" t="n">
         <v>9</v>
       </c>
@@ -988,7 +1026,7 @@
       <c r="G31" s="9" t="n"/>
     </row>
     <row r="32" ht="14.15" customHeight="1">
-      <c r="A32" s="7" t="n">
+      <c r="A32" s="14" t="n">
         <v>17</v>
       </c>
       <c r="B32" s="8" t="inlineStr">
@@ -999,7 +1037,9 @@
       <c r="C32" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D32" s="9" t="n"/>
+      <c r="D32" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E32" s="9" t="n">
         <v>7</v>
       </c>
@@ -1010,7 +1050,7 @@
       <c r="G32" s="9" t="n"/>
     </row>
     <row r="33" ht="14.15" customHeight="1">
-      <c r="A33" s="7" t="n">
+      <c r="A33" s="14" t="n">
         <v>18</v>
       </c>
       <c r="B33" s="8" t="inlineStr">
@@ -1021,7 +1061,9 @@
       <c r="C33" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D33" s="9" t="n"/>
+      <c r="D33" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E33" s="9" t="n">
         <v>6</v>
       </c>
@@ -1032,7 +1074,7 @@
       <c r="G33" s="9" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="10" t="inlineStr">
+      <c r="A34" s="15" t="inlineStr">
         <is>
           <t>Sum</t>
         </is>
@@ -1040,18 +1082,18 @@
       <c r="B34" s="11" t="n"/>
       <c r="C34" s="11" t="n"/>
       <c r="D34" s="12" t="n"/>
-      <c r="E34" s="10">
+      <c r="E34" s="15">
         <f>SUM(E16:E33)</f>
         <v/>
       </c>
-      <c r="F34" s="10">
+      <c r="F34" s="15">
         <f>SUM(F16:F33)</f>
         <v/>
       </c>
       <c r="G34" s="13" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="10" t="inlineStr">
+      <c r="A35" s="15" t="inlineStr">
         <is>
           <t>Score out of 100</t>
         </is>
@@ -1060,7 +1102,7 @@
       <c r="C35" s="11" t="n"/>
       <c r="D35" s="11" t="n"/>
       <c r="E35" s="12" t="n"/>
-      <c r="F35" s="10">
+      <c r="F35" s="15">
         <f>F34/E34*100</f>
         <v/>
       </c>
@@ -1068,7 +1110,7 @@
     </row>
     <row r="36" ht="9.75" customHeight="1"/>
     <row r="37">
-      <c r="A37" s="10" t="inlineStr">
+      <c r="A37" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">Total achieved points out of 30  </t>
         </is>
@@ -1077,11 +1119,11 @@
       <c r="C37" s="11" t="n"/>
       <c r="D37" s="11" t="n"/>
       <c r="E37" s="12" t="n"/>
-      <c r="F37" s="10">
+      <c r="F37" s="15">
         <f>F35*30/100</f>
         <v/>
       </c>
-      <c r="G37" s="10" t="inlineStr">
+      <c r="G37" s="15" t="inlineStr">
         <is>
           <t>Points</t>
         </is>
